--- a/healthcare_forms/010_patient_clinic_registration_form--healthcare_forms.xlsx
+++ b/healthcare_forms/010_patient_clinic_registration_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1217,8 +1217,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'asthma'}</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Asthma'}</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'amlodipine'}</t>
+          <t>amlodipine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Amlodipine'}</t>
+          <t>Amlodipine</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'aspirin'}</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Aspirin'}</t>
+          <t>Aspirin</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'clobetasol'}</t>
+          <t>clobetasol</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Clobetasol'}</t>
+          <t>Clobetasol</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'lisinopril'}</t>
+          <t>lisinopril</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Lisinopril'}</t>
+          <t>Lisinopril</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'child'}</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Child'}</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
